--- a/output/pdf_financials_xlsx/MEGO.P.xlsx
+++ b/output/pdf_financials_xlsx/MEGO.P.xlsx
@@ -2539,16 +2539,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.077413</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.077413</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.077413</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.077413</v>
       </c>
     </row>
     <row r="93">
@@ -3872,7 +3872,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MEGO.P.xlsx
+++ b/output/pdf_financials_xlsx/MEGO.P.xlsx
@@ -632,16 +632,16 @@
         <v>0.000265</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.011247</v>
+        <v>0.134787</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0189</v>
+        <v>0.06725100000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.024886</v>
+        <v>0.093015</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.038476</v>
+        <v>0.070046</v>
       </c>
     </row>
     <row r="11">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.011247</v>
+        <v>-0.134787</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.0189</v>
+        <v>-0.06725100000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.024886</v>
+        <v>-0.093015</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.038476</v>
+        <v>-0.070046</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002974</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.014708</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.037551</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023349</v>
       </c>
     </row>
     <row r="13">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.131813</v>
+        <v>-0.134787</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.052543</v>
+        <v>-0.06725100000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.055464</v>
+        <v>-0.093015</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.046697</v>
+        <v>-0.070046</v>
       </c>
     </row>
     <row r="28">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.131813</v>
+        <v>-0.134787</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.052543</v>
+        <v>-0.06725100000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.055464</v>
+        <v>-0.093015</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.046697</v>
+        <v>-0.070046</v>
       </c>
     </row>
     <row r="30">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5772,16 +5772,16 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.134787</v>
+        <v>0.134787</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.06725100000000001</v>
+        <v>0.06725100000000001</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.093015</v>
+        <v>0.093015</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.070046</v>
+        <v>0.070046</v>
       </c>
     </row>
     <row r="57">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">

--- a/output/pdf_financials_xlsx/MEGO.P.xlsx
+++ b/output/pdf_financials_xlsx/MEGO.P.xlsx
@@ -4693,7 +4693,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5185,7 +5189,11 @@
           <t>Proceeds from share issuances, net 238,488</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.2938</v>
       </c>
